--- a/05_Testovanie/testovacie-scenare.xlsx
+++ b/05_Testovanie/testovacie-scenare.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Papo\source\repos\Rocnikovy_stick_fight\dokumentacia\Stickops\05_Testovanie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{381D42AF-06F8-4D0B-BD44-782AE3CD958A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2DE3794A-9702-45FD-AB89-D1AAC8ECD026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{11593CA5-B242-4B7F-B28E-7B7A24A940DD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EE3EF8F5-8280-46CB-8DA7-D5266124079D}"/>
   </bookViews>
   <sheets>
     <sheet name="Testovacie scenáre" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="184">
   <si>
     <t>ID</t>
   </si>
@@ -68,7 +68,7 @@
     <t>Stav</t>
   </si>
   <si>
-    <t>Automatické testy (spustené 16. 10. 2026: stick_tests 70/70, stick_ai_tests 20/20)</t>
+    <t>Automatické testy (doctest)</t>
   </si>
   <si>
     <t>TC-A01</t>
@@ -80,7 +80,7 @@
     <t>Automatický (doctest)</t>
   </si>
   <si>
-    <t>FR-010</t>
+    <t>FR-013, FR-014, FR-015</t>
   </si>
   <si>
     <t>Zostavená hra (ZOSTAV.bat)</t>
@@ -92,10 +92,7 @@
     <t>test_block.cpp (5 testov): perfektný blok = 0 poškodenia, horšie načasovanie = viac poškodenia, blok zozadu nefunguje, mlátenie bloku nepomôže</t>
   </si>
   <si>
-    <t>Všetky testy skupiny prešli</t>
-  </si>
-  <si>
-    <t>Prešiel</t>
+    <t>Naplánovaný</t>
   </si>
   <si>
     <t>TC-A02</t>
@@ -104,7 +101,7 @@
     <t>Boj, zásahy, kombá</t>
   </si>
   <si>
-    <t>FR-009, FR-014, FR-016</t>
+    <t>FR-009 – FR-012, FR-019, FR-024</t>
   </si>
   <si>
     <t>test_combat.cpp + test_combo.cpp (24 testov): zásah, hitstun, trade, hitstop, kombo jab-cross-hák, cancel, uppercut, žonglovanie, K.O.</t>
@@ -116,7 +113,7 @@
     <t>Načítanie a chyby obsahu</t>
   </si>
   <si>
-    <t>FR-034 – FR-037</t>
+    <t>FR-042 – FR-045</t>
   </si>
   <si>
     <t>test_content.cpp (10 testov): obsah sa načíta bez chýb, chyba hlási riadok a radu po slovensky, BOM, preklep v kľúči s návrhom</t>
@@ -140,7 +137,7 @@
     <t>Úhyb</t>
   </si>
   <si>
-    <t>FR-011</t>
+    <t>FR-016</t>
   </si>
   <si>
     <t>test_dodge.cpp (6 testov): nezraniteľnosť na začiatku, cooldown, záklon dozadu, útok z úhybu</t>
@@ -152,7 +149,7 @@
     <t>Finishery</t>
   </si>
   <si>
-    <t>FR-017</t>
+    <t>FR-025</t>
   </si>
   <si>
     <t>test_finisher.cpp (6 testov): finisher sa spustí sám po poslednom kole, aj pre hráča 2, je deterministický</t>
@@ -176,7 +173,7 @@
     <t>SILA</t>
   </si>
   <si>
-    <t>FR-013</t>
+    <t>FR-022</t>
   </si>
   <si>
     <t>test_power.cpp (4 testy): posilnený úder minie SILU, bez SILY bežný úder, plní sa len hrou, prenáša sa do ďalšieho kola</t>
@@ -188,7 +185,7 @@
     <t>Klinč a skok nohami napred</t>
   </si>
   <si>
-    <t>FR-012</t>
+    <t>FR-021</t>
   </si>
   <si>
     <t>test_action.cpp / test_combat.cpp: O prebije jab, zablokovaný O nechá útočníka otvoreného, klinč prejde cez blok</t>
@@ -200,7 +197,7 @@
     <t>Replay</t>
   </si>
   <si>
-    <t>FR-019</t>
+    <t>FR-027</t>
   </si>
   <si>
     <t>test_replay.cpp (2 testy): prehraný zápas skončí v rovnakom stave, poškodený replay sa odmietne so slovenskou hláškou</t>
@@ -212,7 +209,7 @@
     <t>Ladiaci panel – zápis do JSON</t>
   </si>
   <si>
-    <t>FR-042</t>
+    <t>FR-050</t>
   </si>
   <si>
     <t>test_jsonpatch.cpp (2 testy): zmena čísla zachová komentáre a formát</t>
@@ -224,7 +221,7 @@
     <t>AI bot a sieť</t>
   </si>
   <si>
-    <t>FR-028, FR-030</t>
+    <t>FR-036, FR-038</t>
   </si>
   <si>
     <t>test_ai_bot.cpp (3 testy): bot porazí nečinného súpera, zápas botov je deterministický, sieť vyberie povolenú akciu</t>
@@ -236,7 +233,7 @@
     <t>AI obsah a kampaň</t>
   </si>
   <si>
-    <t>FR-023, FR-024, FR-030</t>
+    <t>FR-031, FR-032, FR-038</t>
   </si>
   <si>
     <t>test_ai_content.cpp (5 testov): ai/content sa načíta, model sa načíta, 25 levelov s bossom každý piaty, odomykanie a uloženie postupu</t>
@@ -248,303 +245,312 @@
     <t>Pozorovanie a odmena AI</t>
   </si>
   <si>
+    <t>FR-036</t>
+  </si>
+  <si>
+    <t>test_ai_env.cpp (5 testov): rozsah pozorovania, zrkadlovosť, reakčný čas, maska akcií bez SILY</t>
+  </si>
+  <si>
+    <t>TC-A15</t>
+  </si>
+  <si>
+    <t>Navigácia AI po plošinkách</t>
+  </si>
+  <si>
+    <t>FR-008, FR-038</t>
+  </si>
+  <si>
+    <t>test_ai_navigation.cpp (3 testy): bossovia vylezú za súperom na najvyššiu plošinku v každej aréne</t>
+  </si>
+  <si>
+    <t>TC-A17</t>
+  </si>
+  <si>
+    <t>Zásahové zóny tela</t>
+  </si>
+  <si>
+    <t>FR-017, FR-018</t>
+  </si>
+  <si>
+    <t>test zón: zásah do hlavy uberá viac a omráči dlhšie ako do trupu, zásah do nôh uberá menej, nízky útok podrazí</t>
+  </si>
+  <si>
+    <t>TC-A16</t>
+  </si>
+  <si>
+    <t>Tréning AI</t>
+  </si>
+  <si>
+    <t>FR-039</t>
+  </si>
+  <si>
+    <t>test_ai_trainer.cpp (4 testy): 5 bossov zoradených podľa sily, deterministický tréning, checkpoint, uloženie siete</t>
+  </si>
+  <si>
+    <t>Manuálne testy</t>
+  </si>
+  <si>
+    <t>TC-M01</t>
+  </si>
+  <si>
+    <t>Hlavné menu</t>
+  </si>
+  <si>
+    <t>Manuálny</t>
+  </si>
+  <si>
+    <t>FR-001 – FR-003</t>
+  </si>
+  <si>
+    <t>Hra je zostavená</t>
+  </si>
+  <si>
+    <t>1. Spustiť HRAJ.bat. 2. Prejsť menu šípkami, Enter, Esc. 3. Kliknúť myšou na položku, pravým klikom späť.</t>
+  </si>
+  <si>
+    <t>Zobrazí sa menu HRAŤ / KOZMETIKA / NASTAVENIA / KONIEC, ovláda sa klávesnicou aj myšou.</t>
+  </si>
+  <si>
+    <t>TC-M02</t>
+  </si>
+  <si>
+    <t>Nastavenie hlasitosti</t>
+  </si>
+  <si>
+    <t>FR-004</t>
+  </si>
+  <si>
+    <t>Hra v hlavnom menu</t>
+  </si>
+  <si>
+    <t>1. NASTAVENIA › Hudba, Zvuky – zmeniť hlasitosť. 2. Ukončiť hru a znova spustiť.</t>
+  </si>
+  <si>
+    <t>Zmena je počuť hneď, po reštarte ostane (game/saves/settings.json).</t>
+  </si>
+  <si>
+    <t>TC-M03</t>
+  </si>
+  <si>
+    <t>Celá obrazovka</t>
+  </si>
+  <si>
+    <t>FR-005</t>
+  </si>
+  <si>
+    <t>Hra beží</t>
+  </si>
+  <si>
+    <t>1. Stlačiť F11 v menu aj v boji. 2. Prepnúť v NASTAVENIA › Celá obrazovka.</t>
+  </si>
+  <si>
+    <t>Okno sa prepína medzi celou obrazovkou a oknom.</t>
+  </si>
+  <si>
+    <t>TC-M04</t>
+  </si>
+  <si>
+    <t>Rýchly zápas proti AI</t>
+  </si>
+  <si>
+    <t>FR-029, FR-037</t>
+  </si>
+  <si>
+    <t>1. HRAŤ › Rýchly zápas. 2. Zvoliť úroveň súpera (Ľahká/Stredná/Ťažká) a arénu. 3. Do boja!</t>
+  </si>
+  <si>
+    <t>Zápas sa spustí s vybraným súperom v zvolenej aréne, nad súperom svieti AI.</t>
+  </si>
+  <si>
+    <t>TC-M05</t>
+  </si>
+  <si>
+    <t>Zápas dvoch hráčov</t>
+  </si>
+  <si>
+    <t>FR-030</t>
+  </si>
+  <si>
+    <t>1. Rýchly zápas › Súper = Hráč 2. 2. Hráč 1 hrá WASD/J/K/L, hráč 2 šípkami a Num klávesmi.</t>
+  </si>
+  <si>
+    <t>Obe postavy sa dajú ovládať naraz, hráč 2 je červený s modrou čelenkou.</t>
+  </si>
+  <si>
+    <t>TC-M06</t>
+  </si>
+  <si>
+    <t>HUD počas boja</t>
+  </si>
+  <si>
+    <t>FR-023</t>
+  </si>
+  <si>
+    <t>Prebieha zápas</t>
+  </si>
+  <si>
+    <t>1. Zasiahnuť súpera. 2. Sledovať HUD.</t>
+  </si>
+  <si>
+    <t>Zdravie a SILA sa menia, beží čas kola, zobrazujú sa vyhraté kolá.</t>
+  </si>
+  <si>
+    <t>TC-M07</t>
+  </si>
+  <si>
+    <t>Koniec kola časom</t>
+  </si>
+  <si>
+    <t>FR-024</t>
+  </si>
+  <si>
+    <t>1. Nechať uplynúť čas kola.</t>
+  </si>
+  <si>
+    <t>Kolo vyhrá bojovník s viac zdravím.</t>
+  </si>
+  <si>
+    <t>TC-M08</t>
+  </si>
+  <si>
+    <t>Pauza</t>
+  </si>
+  <si>
+    <t>FR-026</t>
+  </si>
+  <si>
+    <t>1. Stlačiť Esc. 2. Vyskúšať Pokračovať, Odznova, Ovládanie, Hlavné menu.</t>
+  </si>
+  <si>
+    <t>Simulácia stojí, hudba je stlmená, každá voľba spraví popísanú akciu.</t>
+  </si>
+  <si>
+    <t>TC-M09</t>
+  </si>
+  <si>
+    <t>Kampaň – odomknutie levelu</t>
+  </si>
+  <si>
+    <t>FR-031, FR-032</t>
+  </si>
+  <si>
+    <t>Nový postup</t>
+  </si>
+  <si>
+    <t>1. HRAŤ › Kampaň. 2. Vyhrať level 1. 3. Ukončiť a spustiť hru.</t>
+  </si>
+  <si>
+    <t>Level 2 je odomknutý aj po reštarte (ai/saves/progress.json).</t>
+  </si>
+  <si>
+    <t>TC-M10</t>
+  </si>
+  <si>
+    <t>Kampaň – boss a presila</t>
+  </si>
+  <si>
+    <t>FR-033, FR-038</t>
+  </si>
+  <si>
+    <t>Odomknuté levely 4 a 5</t>
+  </si>
+  <si>
+    <t>1. Zahrať presilu. 2. Zahrať level 5 (boss kapitoly 1).</t>
+  </si>
+  <si>
+    <t>V presile prichádzajú súperi po sebe bez obnovy zdravia; boss má vlastný štýl.</t>
+  </si>
+  <si>
+    <t>TC-M11</t>
+  </si>
+  <si>
+    <t>Zmazanie postupu</t>
+  </si>
+  <si>
+    <t>FR-032</t>
+  </si>
+  <si>
+    <t>Existuje postup</t>
+  </si>
+  <si>
+    <t>1. Na obrazovke kampane podržať DELETE.</t>
+  </si>
+  <si>
+    <t>Postup sa zmaže, odomknutý je len level 1.</t>
+  </si>
+  <si>
+    <t>TC-M12</t>
+  </si>
+  <si>
+    <t>Kozmetika – výber finishera</t>
+  </si>
+  <si>
+    <t>FR-034, FR-025</t>
+  </si>
+  <si>
+    <t>Odomknutý aspoň jeden finisher bossa</t>
+  </si>
+  <si>
+    <t>1. KOZMETIKA. 2. Vybrať finisher. 3. Vyhrať zápas.</t>
+  </si>
+  <si>
+    <t>Náhľad ukáže finisher, po poslednom kole sa prehrá zvolený finisher.</t>
+  </si>
+  <si>
+    <t>TC-M13</t>
+  </si>
+  <si>
+    <t>Posledný replay</t>
+  </si>
+  <si>
+    <t>Dohraný aspoň jeden zápas</t>
+  </si>
+  <si>
+    <t>1. HRAŤ › Posledný replay.</t>
+  </si>
+  <si>
+    <t>Prehrá sa posledný zápas presne rovnako.</t>
+  </si>
+  <si>
+    <t>TC-M14</t>
+  </si>
+  <si>
+    <t>Chyba v obsahu</t>
+  </si>
+  <si>
+    <t>FR-043</t>
+  </si>
+  <si>
+    <t>1. V game/content/arenas/dojo.json zmazať čiarku. 2. Stlačiť F5.</t>
+  </si>
+  <si>
+    <t>Hra nespadne, zobrazí hlášku po slovensky so súborom, riadkom a návrhom opravy.</t>
+  </si>
+  <si>
+    <t>TC-M15</t>
+  </si>
+  <si>
+    <t>Načítanie zmien za behu</t>
+  </si>
+  <si>
+    <t>FR-046</t>
+  </si>
+  <si>
+    <t>1. Zmeniť poškodenie útoku v game/content/moves. 2. F5.</t>
+  </si>
+  <si>
+    <t>Nová hodnota platí bez reštartu hry.</t>
+  </si>
+  <si>
+    <t>TC-M16</t>
+  </si>
+  <si>
+    <t>Gamepad</t>
+  </si>
+  <si>
     <t>FR-028</t>
   </si>
   <si>
-    <t>test_ai_env.cpp (5 testov): rozsah pozorovania, zrkadlovosť, reakčný čas, maska akcií bez SILY</t>
-  </si>
-  <si>
-    <t>TC-A15</t>
-  </si>
-  <si>
-    <t>Navigácia AI po plošinkách</t>
-  </si>
-  <si>
-    <t>FR-008, FR-030</t>
-  </si>
-  <si>
-    <t>test_ai_navigation.cpp (3 testy): bossovia vylezú za súperom na najvyššiu plošinku v každej aréne</t>
-  </si>
-  <si>
-    <t>TC-A16</t>
-  </si>
-  <si>
-    <t>Tréning AI</t>
-  </si>
-  <si>
-    <t>FR-031</t>
-  </si>
-  <si>
-    <t>test_ai_trainer.cpp (4 testy): 5 bossov zoradených podľa sily, deterministický tréning, checkpoint, uloženie siete</t>
-  </si>
-  <si>
-    <t>Manuálne testy</t>
-  </si>
-  <si>
-    <t>TC-M01</t>
-  </si>
-  <si>
-    <t>Hlavné menu</t>
-  </si>
-  <si>
-    <t>Manuálny</t>
-  </si>
-  <si>
-    <t>FR-001 – FR-003</t>
-  </si>
-  <si>
-    <t>Hra je zostavená</t>
-  </si>
-  <si>
-    <t>1. Spustiť HRAJ.bat. 2. Prejsť menu šípkami, Enter, Esc. 3. Kliknúť myšou na položku, pravým klikom späť.</t>
-  </si>
-  <si>
-    <t>Zobrazí sa menu HRAŤ / KOZMETIKA / NASTAVENIA / KONIEC, ovláda sa klávesnicou aj myšou.</t>
-  </si>
-  <si>
-    <t>Čaká na manuálny test</t>
-  </si>
-  <si>
-    <t>TC-M02</t>
-  </si>
-  <si>
-    <t>Nastavenie hlasitosti</t>
-  </si>
-  <si>
-    <t>FR-004</t>
-  </si>
-  <si>
-    <t>Hra v hlavnom menu</t>
-  </si>
-  <si>
-    <t>1. NASTAVENIA › Hudba, Zvuky – zmeniť hlasitosť. 2. Ukončiť hru a znova spustiť.</t>
-  </si>
-  <si>
-    <t>Zmena je počuť hneď, po reštarte ostane (game/saves/settings.json).</t>
-  </si>
-  <si>
-    <t>TC-M03</t>
-  </si>
-  <si>
-    <t>Celá obrazovka</t>
-  </si>
-  <si>
-    <t>FR-005</t>
-  </si>
-  <si>
-    <t>Hra beží</t>
-  </si>
-  <si>
-    <t>1. Stlačiť F11 v menu aj v boji. 2. Prepnúť v NASTAVENIA › Celá obrazovka.</t>
-  </si>
-  <si>
-    <t>Okno sa prepína medzi celou obrazovkou a oknom.</t>
-  </si>
-  <si>
-    <t>TC-M04</t>
-  </si>
-  <si>
-    <t>Rýchly zápas proti AI</t>
-  </si>
-  <si>
-    <t>FR-021, FR-029</t>
-  </si>
-  <si>
-    <t>1. HRAŤ › Rýchly zápas. 2. Zvoliť súpera a arénu. 3. Do boja!</t>
-  </si>
-  <si>
-    <t>Zápas sa spustí s vybraným súperom v zvolenej aréne, nad súperom svieti AI.</t>
-  </si>
-  <si>
-    <t>TC-M05</t>
-  </si>
-  <si>
-    <t>Zápas dvoch hráčov</t>
-  </si>
-  <si>
-    <t>FR-022</t>
-  </si>
-  <si>
-    <t>1. Rýchly zápas › Súper = Hráč 2. 2. Hráč 1 hrá WASD/J/K/L, hráč 2 šípkami a Num klávesmi.</t>
-  </si>
-  <si>
-    <t>Obe postavy sa dajú ovládať naraz, hráč 2 je červený s modrou čelenkou.</t>
-  </si>
-  <si>
-    <t>TC-M06</t>
-  </si>
-  <si>
-    <t>HUD počas boja</t>
-  </si>
-  <si>
-    <t>FR-015</t>
-  </si>
-  <si>
-    <t>Prebieha zápas</t>
-  </si>
-  <si>
-    <t>1. Zasiahnuť súpera. 2. Sledovať HUD.</t>
-  </si>
-  <si>
-    <t>Zdravie a SILA sa menia, beží čas kola, zobrazujú sa vyhraté kolá.</t>
-  </si>
-  <si>
-    <t>TC-M07</t>
-  </si>
-  <si>
-    <t>Koniec kola časom</t>
-  </si>
-  <si>
-    <t>FR-016</t>
-  </si>
-  <si>
-    <t>1. Nechať uplynúť čas kola.</t>
-  </si>
-  <si>
-    <t>Kolo vyhrá bojovník s viac zdravím.</t>
-  </si>
-  <si>
-    <t>TC-M08</t>
-  </si>
-  <si>
-    <t>Pauza</t>
-  </si>
-  <si>
-    <t>FR-018</t>
-  </si>
-  <si>
-    <t>1. Stlačiť Esc. 2. Vyskúšať Pokračovať, Odznova, Ovládanie, Hlavné menu.</t>
-  </si>
-  <si>
-    <t>Simulácia stojí, hudba je stlmená, každá voľba spraví popísanú akciu.</t>
-  </si>
-  <si>
-    <t>TC-M09</t>
-  </si>
-  <si>
-    <t>Kampaň – odomknutie levelu</t>
-  </si>
-  <si>
-    <t>FR-023, FR-024</t>
-  </si>
-  <si>
-    <t>Nový postup</t>
-  </si>
-  <si>
-    <t>1. HRAŤ › Kampaň. 2. Vyhrať level 1. 3. Ukončiť a spustiť hru.</t>
-  </si>
-  <si>
-    <t>Level 2 je odomknutý aj po reštarte (ai/saves/progress.json).</t>
-  </si>
-  <si>
-    <t>TC-M10</t>
-  </si>
-  <si>
-    <t>Kampaň – boss a presila</t>
-  </si>
-  <si>
-    <t>FR-025, FR-030</t>
-  </si>
-  <si>
-    <t>Odomknuté levely 4 a 5</t>
-  </si>
-  <si>
-    <t>1. Zahrať presilu. 2. Zahrať level 5 (boss Hromotĺk).</t>
-  </si>
-  <si>
-    <t>V presile prichádzajú súperi po sebe bez obnovy zdravia; boss má vlastný štýl.</t>
-  </si>
-  <si>
-    <t>TC-M11</t>
-  </si>
-  <si>
-    <t>Zmazanie postupu</t>
-  </si>
-  <si>
-    <t>FR-024</t>
-  </si>
-  <si>
-    <t>Existuje postup</t>
-  </si>
-  <si>
-    <t>1. Na obrazovke kampane podržať DELETE.</t>
-  </si>
-  <si>
-    <t>Postup sa zmaže, odomknutý je len level 1.</t>
-  </si>
-  <si>
-    <t>TC-M12</t>
-  </si>
-  <si>
-    <t>Kozmetika – výber finishera</t>
-  </si>
-  <si>
-    <t>FR-026, FR-017</t>
-  </si>
-  <si>
-    <t>Odomknutý aspoň jeden finisher bossa</t>
-  </si>
-  <si>
-    <t>1. KOZMETIKA. 2. Vybrať finisher. 3. Vyhrať zápas.</t>
-  </si>
-  <si>
-    <t>Náhľad ukáže finisher, po poslednom kole sa prehrá zvolený finisher.</t>
-  </si>
-  <si>
-    <t>TC-M13</t>
-  </si>
-  <si>
-    <t>Posledný replay</t>
-  </si>
-  <si>
-    <t>Dohraný aspoň jeden zápas</t>
-  </si>
-  <si>
-    <t>1. HRAŤ › Posledný replay.</t>
-  </si>
-  <si>
-    <t>Prehrá sa posledný zápas presne rovnako.</t>
-  </si>
-  <si>
-    <t>TC-M14</t>
-  </si>
-  <si>
-    <t>Chyba v obsahu</t>
-  </si>
-  <si>
-    <t>FR-035</t>
-  </si>
-  <si>
-    <t>1. V game/content/arenas/dojo.json zmazať čiarku. 2. Stlačiť F5.</t>
-  </si>
-  <si>
-    <t>Hra nespadne, zobrazí hlášku po slovensky so súborom, riadkom a návrhom opravy.</t>
-  </si>
-  <si>
-    <t>TC-M15</t>
-  </si>
-  <si>
-    <t>Načítanie zmien za behu</t>
-  </si>
-  <si>
-    <t>FR-038</t>
-  </si>
-  <si>
-    <t>1. Zmeniť poškodenie útoku v game/content/moves. 2. F5.</t>
-  </si>
-  <si>
-    <t>Nová hodnota platí bez reštartu hry.</t>
-  </si>
-  <si>
-    <t>TC-M16</t>
-  </si>
-  <si>
-    <t>Gamepad</t>
-  </si>
-  <si>
-    <t>FR-020</t>
-  </si>
-  <si>
     <t>Pripojený gamepad</t>
   </si>
   <si>
@@ -560,7 +566,7 @@
     <t>Tréning bossa</t>
   </si>
   <si>
-    <t>FR-031, FR-032</t>
+    <t>FR-039, FR-040</t>
   </si>
   <si>
     <t>Zostavené nástroje</t>
@@ -578,7 +584,7 @@
     <t>Kontrola obsahu</t>
   </si>
   <si>
-    <t>FR-036</t>
+    <t>FR-044</t>
   </si>
   <si>
     <t>1. TRENER.bat › 1 Skontrolovať obsah.</t>
@@ -1008,8 +1014,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35A7D43E-9240-4361-805B-440F4DA6A42C}">
-  <dimension ref="A1:I37"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{090DC8D6-0D9D-4478-B223-50FBB0390D68}">
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
@@ -1052,7 +1058,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
         <v>9</v>
@@ -1087,25 +1093,23 @@
       <c r="G3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="H3" s="3"/>
       <c r="I3" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>20</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>14</v>
@@ -1114,27 +1118,25 @@
         <v>15</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>14</v>
@@ -1143,27 +1145,25 @@
         <v>15</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="H5" s="3"/>
       <c r="I5" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>14</v>
@@ -1172,27 +1172,25 @@
         <v>15</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="H6" s="3"/>
       <c r="I6" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>14</v>
@@ -1201,27 +1199,25 @@
         <v>15</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="H7" s="3"/>
       <c r="I7" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>14</v>
@@ -1230,27 +1226,25 @@
         <v>15</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="H8" s="3"/>
       <c r="I8" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>14</v>
@@ -1259,27 +1253,25 @@
         <v>15</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="H9" s="3"/>
       <c r="I9" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>14</v>
@@ -1288,27 +1280,25 @@
         <v>15</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="H10" s="3"/>
       <c r="I10" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>14</v>
@@ -1317,27 +1307,25 @@
         <v>15</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>14</v>
@@ -1346,27 +1334,25 @@
         <v>15</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="H12" s="3"/>
       <c r="I12" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>14</v>
@@ -1375,27 +1361,25 @@
         <v>15</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="H13" s="3"/>
       <c r="I13" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>14</v>
@@ -1404,27 +1388,25 @@
         <v>15</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="H14" s="3"/>
       <c r="I14" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>14</v>
@@ -1433,27 +1415,25 @@
         <v>15</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="H15" s="3"/>
       <c r="I15" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>14</v>
@@ -1462,27 +1442,25 @@
         <v>15</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="H16" s="3"/>
       <c r="I16" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>14</v>
@@ -1491,27 +1469,25 @@
         <v>15</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>17</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="H17" s="3"/>
       <c r="I17" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>14</v>
@@ -1520,512 +1496,537 @@
         <v>15</v>
       </c>
       <c r="G18" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="20" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="C19" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="E19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="H19" s="3"/>
+      <c r="I19" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+    </row>
+    <row r="21" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="B21" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3" t="s">
+      <c r="E21" s="3" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="F21" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="G21" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="G22" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="G23" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>109</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="G25" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>115</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="G26" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="G27" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>125</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="G28" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="G29" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="G30" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="G31" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="G32" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>154</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="G33" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>159</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="G34" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>164</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="G35" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="G36" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>176</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="G37" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>181</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3" t="s">
-        <v>87</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
